--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487683_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487683_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9188</v>
+        <v>6.128</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9221</v>
+        <v>4.0222</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9968</v>
+        <v>2.1058</v>
       </c>
       <c r="G2" t="n">
         <v>5.3915</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.801</v>
+        <v>-0.5919</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1694</v>
+        <v>-0.0693</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6317</v>
+        <v>-0.5226</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6119</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>P. TOMICO RUIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1829</v>
+        <v>5.4937</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2586</v>
+        <v>3.0089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9243</v>
+        <v>2.4847</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5928</v>
+        <v>3.0792</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5318</v>
+        <v>1.7968</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0611</v>
+        <v>1.2824</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5409</v>
+        <v>3.6146</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9783</v>
+        <v>1.5036</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5626</v>
+        <v>2.111</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9481</v>
+        <v>-0.5354</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4466</v>
+        <v>0.2933</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5015</v>
+        <v>-0.8286</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>2.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-1.1558</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8479</v>
+        <v>-0.6057</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1559</v>
+        <v>-0.5501</v>
       </c>
       <c r="V3" t="n">
-        <v>1.506</v>
+        <v>0.6597</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. TOMICO RUIZ</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0788</v>
+        <v>4.9709</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9484</v>
+        <v>4.3192</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1304</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0792</v>
+        <v>3.5928</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7968</v>
+        <v>2.5318</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2824</v>
+        <v>1.0611</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6146</v>
+        <v>5.5409</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5036</v>
+        <v>2.9783</v>
       </c>
       <c r="L4" t="n">
-        <v>2.111</v>
+        <v>2.5626</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5354</v>
+        <v>-1.9481</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2933</v>
+        <v>-0.4466</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8286</v>
+        <v>-1.5015</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9105</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9105</v>
+        <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5706</v>
+        <v>-0.904</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6662</v>
+        <v>-0.7874</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9044</v>
+        <v>-0.1166</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6597</v>
+        <v>1.506</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8823</v>
+        <v>4.3184</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9914</v>
+        <v>3.591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8909</v>
+        <v>0.7274</v>
       </c>
       <c r="G5" t="n">
         <v>4.8012</v>
@@ -844,13 +844,13 @@
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0249</v>
+        <v>-0.5888</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3163</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3412</v>
+        <v>-0.5047</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2821</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1066</v>
+        <v>4.2701</v>
       </c>
       <c r="E6" t="n">
         <v>3.7758</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3308</v>
+        <v>0.4943</v>
       </c>
       <c r="G6" t="n">
         <v>5.5901</v>
@@ -922,13 +922,13 @@
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4073</v>
+        <v>-1.2438</v>
       </c>
       <c r="T6" t="n">
         <v>-0.4116</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9957</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0.894</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.0062</v>
+        <v>4.2698</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6754</v>
+        <v>5.7755</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6692</v>
+        <v>-1.5057</v>
       </c>
       <c r="G7" t="n">
         <v>4.3482</v>
@@ -1000,13 +1000,13 @@
         <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1763</v>
+        <v>-0.9127</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4116</v>
+        <v>-0.3115</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7647</v>
+        <v>-0.6011</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3299</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6973</v>
+        <v>2.9337</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4764</v>
+        <v>1.5765</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2209</v>
+        <v>1.3572</v>
       </c>
       <c r="G8" t="n">
         <v>1.6359</v>
@@ -1078,13 +1078,13 @@
         <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2191</v>
+        <v>-0.9828</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8557</v>
+        <v>-0.7195</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0478</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2624</v>
+        <v>2.541</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2416</v>
+        <v>2.3021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0208</v>
+        <v>0.2389</v>
       </c>
       <c r="G9" t="n">
         <v>3.7658</v>
@@ -1156,13 +1156,13 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7272</v>
+        <v>-0.4486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6057</v>
+        <v>-0.5451</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1216</v>
+        <v>0.0965</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3187</v>
+        <v>0.2886</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2596</v>
+        <v>-1.0989</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5783</v>
+        <v>1.3875</v>
       </c>
       <c r="G10" t="n">
         <v>1.0215</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4311</v>
+        <v>-0.4612</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>-0.445</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1745</v>
+        <v>-0.0162</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6338</v>
+        <v>-1.9002</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2823</v>
+        <v>-1.2217</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3515</v>
+        <v>-0.6785</v>
       </c>
       <c r="G11" t="n">
         <v>-1.388</v>
@@ -1312,13 +1312,13 @@
         <v>2.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6801</v>
+        <v>-0.9466</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6662</v>
+        <v>-0.6057</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0139</v>
+        <v>-0.3409</v>
       </c>
       <c r="V11" t="n">
         <v>-1.506</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5243</v>
+        <v>-2.7151</v>
       </c>
       <c r="E12" t="n">
         <v>-1.642</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8823</v>
+        <v>-1.073</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3486</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.31</v>
+        <v>-0.5008</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2905</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0195</v>
+        <v>-0.2103</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4477</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30.2959</v>
+        <v>30.59890000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>24.1058</v>
+        <v>24.4086</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1902</v>
+        <v>6.190300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>31.48960000000001</v>
@@ -1465,16 +1465,16 @@
         <v>-14.5525</v>
       </c>
       <c r="R13" t="n">
-        <v>25.22429999999999</v>
+        <v>25.2243</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.0396</v>
+        <v>-8.737</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7219</v>
+        <v>-4.4192</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.318</v>
+        <v>-4.3177</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8254</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3648</v>
+        <v>4.8286</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6959</v>
+        <v>4.9962</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3311</v>
+        <v>-0.1675</v>
       </c>
       <c r="G14" t="n">
         <v>2.8852</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0727</v>
+        <v>0.3911</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1817</v>
+        <v>0.1186</v>
       </c>
       <c r="U14" t="n">
-        <v>0.109</v>
+        <v>0.2725</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4818</v>
+        <v>0.5719</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1421</v>
+        <v>0.8963</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6602</v>
+        <v>-0.3244</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5377</v>
+        <v>0.9516</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6764</v>
+        <v>-0.8058</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8613</v>
+        <v>1.7573</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3135</v>
+        <v>3.0335</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2729</v>
+        <v>0.4531</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0406</v>
+        <v>2.5804</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8512</v>
+        <v>-2.082</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9493</v>
+        <v>-1.2589</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9019</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5523</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3613</v>
+        <v>0.6368</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8286</v>
+        <v>-0.0446</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.6814</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.894</v>
+        <v>1.506</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1194</v>
+        <v>-0.0864</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3958</v>
+        <v>2.4404</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5152</v>
+        <v>-2.5268</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9516</v>
+        <v>-2.5377</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8058</v>
+        <v>-0.6764</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7573</v>
+        <v>-1.8613</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0335</v>
+        <v>1.3135</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4531</v>
+        <v>1.2729</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5804</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.082</v>
+        <v>-3.8512</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2589</v>
+        <v>-1.9493</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-1.9019</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5224</v>
+        <v>1.5523</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0545</v>
+        <v>1.7931</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5451</v>
+        <v>1.1269</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4906</v>
+        <v>0.6662</v>
       </c>
       <c r="V16" t="n">
-        <v>1.506</v>
+        <v>-0.894</v>
       </c>
       <c r="W16" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3235</v>
+        <v>-1.05</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5817</v>
+        <v>1.1823</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9052</v>
+        <v>-2.2323</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7438</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6905</v>
+        <v>0.964</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6662</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3567</v>
+        <v>1.0296</v>
       </c>
       <c r="V17" t="n">
         <v>0.894</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6439</v>
+        <v>-1.3558</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0526</v>
+        <v>0.0475</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5913</v>
+        <v>-1.4034</v>
       </c>
       <c r="G18" t="n">
         <v>-4.9379</v>
@@ -1858,13 +1858,13 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7282999999999999</v>
+        <v>1.0164</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4621</v>
+        <v>0.5622</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2663</v>
+        <v>0.4542</v>
       </c>
       <c r="V18" t="n">
         <v>3.3418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5621</v>
+        <v>-3.3624</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4789</v>
+        <v>-1.9794</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0832</v>
+        <v>-1.383</v>
       </c>
       <c r="G19" t="n">
         <v>-5.1009</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8493</v>
+        <v>1.049</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.4708</v>
       </c>
       <c r="U19" t="n">
-        <v>0.878</v>
+        <v>0.5782</v>
       </c>
       <c r="V19" t="n">
         <v>1.2716</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5186</v>
+        <v>-3.9185</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4187</v>
+        <v>-0.5188</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0999</v>
+        <v>-3.3997</v>
       </c>
       <c r="G20" t="n">
         <v>0.0931</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1943</v>
+        <v>0.7944</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1222</v>
+        <v>0.0221</v>
       </c>
       <c r="U20" t="n">
-        <v>1.072</v>
+        <v>0.7722</v>
       </c>
       <c r="V20" t="n">
         <v>-3.0597</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8224</v>
+        <v>-4.4921</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8077</v>
+        <v>-2.2086</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0147</v>
+        <v>-2.2835</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.671</v>
+        <v>-4.7191</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9435</v>
+        <v>-1.8941</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2725</v>
+        <v>-2.8251</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3141</v>
+        <v>-0.9516</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9516</v>
+        <v>0.3831</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3625</v>
+        <v>-1.3347</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9851</v>
+        <v>-3.7676</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.8951</v>
+        <v>-2.2772</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.09</v>
+        <v>-1.4904</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.2985</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8508</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7591</v>
+        <v>0.7315</v>
       </c>
       <c r="T21" t="n">
-        <v>0.729</v>
+        <v>0.6833</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0301</v>
+        <v>0.0482</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6119</v>
+        <v>0.6597</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8347</v>
+        <v>-4.8774</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3087</v>
+        <v>-2.108</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.526</v>
+        <v>-2.7694</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.7191</v>
+        <v>-1.671</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8941</v>
+        <v>-1.9435</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8251</v>
+        <v>0.2725</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9516</v>
+        <v>2.3141</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3831</v>
+        <v>0.9516</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3347</v>
+        <v>1.3625</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.7676</v>
+        <v>-3.9851</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2772</v>
+        <v>-2.8951</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4904</v>
+        <v>-1.09</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1642</v>
+        <v>-3.2985</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3889</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.4287</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1943</v>
+        <v>0.2754</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6597</v>
+        <v>-0.6119</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6597</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.069</v>
+        <v>-5.5446</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3809</v>
+        <v>-2.1807</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6881</v>
+        <v>-3.3639</v>
       </c>
       <c r="G23" t="n">
         <v>-7.1675</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3223</v>
+        <v>0.8468</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4621</v>
+        <v>0.6623</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1397</v>
+        <v>0.1845</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.249</v>
+        <v>-10.342</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.5583</v>
+        <v>-6.7575</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6907</v>
+        <v>-3.5845</v>
       </c>
       <c r="G24" t="n">
         <v>-7.5415</v>
@@ -2326,13 +2326,13 @@
         <v>1.5523</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.127</v>
+        <v>0.78</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4475</v>
+        <v>0.3533</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3206</v>
+        <v>0.4268</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-30.296</v>
+        <v>-29.6287</v>
       </c>
       <c r="E25" t="n">
         <v>-6.190300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-24.1056</v>
+        <v>-23.4384</v>
       </c>
       <c r="G25" t="n">
         <v>-31.4895</v>
@@ -2377,7 +2377,7 @@
         <v>-9.426200000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>5.632500000000002</v>
+        <v>5.6325</v>
       </c>
       <c r="K25" t="n">
         <v>0.7661999999999994</v>
@@ -2404,13 +2404,13 @@
         <v>14.5525</v>
       </c>
       <c r="S25" t="n">
-        <v>9.0398</v>
+        <v>9.7072</v>
       </c>
       <c r="T25" t="n">
         <v>4.318000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>4.722099999999999</v>
+        <v>5.389200000000001</v>
       </c>
       <c r="V25" t="n">
         <v>2.8254</v>
